--- a/artfynd/A 38326-2025 artfynd.xlsx
+++ b/artfynd/A 38326-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136721966</v>
       </c>
       <c r="B2" t="n">
-        <v>93420</v>
+        <v>93425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136721987</v>
       </c>
       <c r="B3" t="n">
-        <v>93420</v>
+        <v>93425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136721968</v>
       </c>
       <c r="B4" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136721978</v>
       </c>
       <c r="B5" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136721964</v>
       </c>
       <c r="B6" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136721965</v>
       </c>
       <c r="B7" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>136721967</v>
       </c>
       <c r="B8" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>136721970</v>
       </c>
       <c r="B9" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>136721971</v>
       </c>
       <c r="B10" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>136721972</v>
       </c>
       <c r="B11" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136721973</v>
       </c>
       <c r="B12" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>136721974</v>
       </c>
       <c r="B13" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>136721975</v>
       </c>
       <c r="B14" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>136721976</v>
       </c>
       <c r="B15" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>136721977</v>
       </c>
       <c r="B16" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136721979</v>
       </c>
       <c r="B17" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>136721980</v>
       </c>
       <c r="B18" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>136721981</v>
       </c>
       <c r="B19" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>136721982</v>
       </c>
       <c r="B20" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>136721983</v>
       </c>
       <c r="B21" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>136721984</v>
       </c>
       <c r="B22" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>136721985</v>
       </c>
       <c r="B23" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>136721986</v>
       </c>
       <c r="B24" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 38326-2025 artfynd.xlsx
+++ b/artfynd/A 38326-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136721966</v>
       </c>
       <c r="B2" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136721987</v>
       </c>
       <c r="B3" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136721968</v>
       </c>
       <c r="B4" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136721978</v>
       </c>
       <c r="B5" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136721964</v>
       </c>
       <c r="B6" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136721965</v>
       </c>
       <c r="B7" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>136721967</v>
       </c>
       <c r="B8" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>136721970</v>
       </c>
       <c r="B9" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>136721971</v>
       </c>
       <c r="B10" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>136721972</v>
       </c>
       <c r="B11" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136721973</v>
       </c>
       <c r="B12" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>136721974</v>
       </c>
       <c r="B13" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>136721975</v>
       </c>
       <c r="B14" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>136721976</v>
       </c>
       <c r="B15" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>136721977</v>
       </c>
       <c r="B16" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136721979</v>
       </c>
       <c r="B17" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>136721980</v>
       </c>
       <c r="B18" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>136721981</v>
       </c>
       <c r="B19" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>136721982</v>
       </c>
       <c r="B20" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>136721983</v>
       </c>
       <c r="B21" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>136721984</v>
       </c>
       <c r="B22" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>136721985</v>
       </c>
       <c r="B23" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>136721986</v>
       </c>
       <c r="B24" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 38326-2025 artfynd.xlsx
+++ b/artfynd/A 38326-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136721966</v>
       </c>
       <c r="B2" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136721987</v>
       </c>
       <c r="B3" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136721968</v>
       </c>
       <c r="B4" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136721978</v>
       </c>
       <c r="B5" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136721964</v>
       </c>
       <c r="B6" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136721965</v>
       </c>
       <c r="B7" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>136721967</v>
       </c>
       <c r="B8" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>136721970</v>
       </c>
       <c r="B9" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>136721971</v>
       </c>
       <c r="B10" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>136721972</v>
       </c>
       <c r="B11" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136721973</v>
       </c>
       <c r="B12" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>136721974</v>
       </c>
       <c r="B13" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>136721975</v>
       </c>
       <c r="B14" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>136721976</v>
       </c>
       <c r="B15" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>136721977</v>
       </c>
       <c r="B16" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136721979</v>
       </c>
       <c r="B17" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>136721980</v>
       </c>
       <c r="B18" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>136721981</v>
       </c>
       <c r="B19" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>136721982</v>
       </c>
       <c r="B20" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>136721983</v>
       </c>
       <c r="B21" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>136721984</v>
       </c>
       <c r="B22" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>136721985</v>
       </c>
       <c r="B23" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>136721986</v>
       </c>
       <c r="B24" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 38326-2025 artfynd.xlsx
+++ b/artfynd/A 38326-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136721966</v>
       </c>
       <c r="B2" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136721987</v>
       </c>
       <c r="B3" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136721968</v>
       </c>
       <c r="B4" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136721978</v>
       </c>
       <c r="B5" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136721964</v>
       </c>
       <c r="B6" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136721965</v>
       </c>
       <c r="B7" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>136721967</v>
       </c>
       <c r="B8" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>136721970</v>
       </c>
       <c r="B9" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>136721971</v>
       </c>
       <c r="B10" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>136721972</v>
       </c>
       <c r="B11" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136721973</v>
       </c>
       <c r="B12" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>136721974</v>
       </c>
       <c r="B13" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>136721975</v>
       </c>
       <c r="B14" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>136721976</v>
       </c>
       <c r="B15" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>136721977</v>
       </c>
       <c r="B16" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136721979</v>
       </c>
       <c r="B17" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>136721980</v>
       </c>
       <c r="B18" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>136721981</v>
       </c>
       <c r="B19" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>136721982</v>
       </c>
       <c r="B20" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>136721983</v>
       </c>
       <c r="B21" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>136721984</v>
       </c>
       <c r="B22" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>136721985</v>
       </c>
       <c r="B23" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>136721986</v>
       </c>
       <c r="B24" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 38326-2025 artfynd.xlsx
+++ b/artfynd/A 38326-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136721966</v>
       </c>
       <c r="B2" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136721987</v>
       </c>
       <c r="B3" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136721968</v>
       </c>
       <c r="B4" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136721978</v>
       </c>
       <c r="B5" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136721964</v>
       </c>
       <c r="B6" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136721965</v>
       </c>
       <c r="B7" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>136721967</v>
       </c>
       <c r="B8" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>136721970</v>
       </c>
       <c r="B9" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>136721971</v>
       </c>
       <c r="B10" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>136721972</v>
       </c>
       <c r="B11" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136721973</v>
       </c>
       <c r="B12" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>136721974</v>
       </c>
       <c r="B13" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>136721975</v>
       </c>
       <c r="B14" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>136721976</v>
       </c>
       <c r="B15" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>136721977</v>
       </c>
       <c r="B16" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136721979</v>
       </c>
       <c r="B17" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>136721980</v>
       </c>
       <c r="B18" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>136721981</v>
       </c>
       <c r="B19" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>136721982</v>
       </c>
       <c r="B20" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>136721983</v>
       </c>
       <c r="B21" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>136721984</v>
       </c>
       <c r="B22" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>136721985</v>
       </c>
       <c r="B23" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>136721986</v>
       </c>
       <c r="B24" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 38326-2025 artfynd.xlsx
+++ b/artfynd/A 38326-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136721966</v>
       </c>
       <c r="B2" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136721987</v>
       </c>
       <c r="B3" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136721968</v>
       </c>
       <c r="B4" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136721978</v>
       </c>
       <c r="B5" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136721964</v>
       </c>
       <c r="B6" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136721965</v>
       </c>
       <c r="B7" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>136721967</v>
       </c>
       <c r="B8" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>136721970</v>
       </c>
       <c r="B9" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>136721971</v>
       </c>
       <c r="B10" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>136721972</v>
       </c>
       <c r="B11" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136721973</v>
       </c>
       <c r="B12" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>136721974</v>
       </c>
       <c r="B13" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>136721975</v>
       </c>
       <c r="B14" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>136721976</v>
       </c>
       <c r="B15" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>136721977</v>
       </c>
       <c r="B16" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136721979</v>
       </c>
       <c r="B17" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>136721980</v>
       </c>
       <c r="B18" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>136721981</v>
       </c>
       <c r="B19" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>136721982</v>
       </c>
       <c r="B20" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>136721983</v>
       </c>
       <c r="B21" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>136721984</v>
       </c>
       <c r="B22" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>136721985</v>
       </c>
       <c r="B23" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>136721986</v>
       </c>
       <c r="B24" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 38326-2025 artfynd.xlsx
+++ b/artfynd/A 38326-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136721966</v>
       </c>
       <c r="B2" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136721987</v>
       </c>
       <c r="B3" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136721968</v>
       </c>
       <c r="B4" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136721978</v>
       </c>
       <c r="B5" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136721964</v>
       </c>
       <c r="B6" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136721965</v>
       </c>
       <c r="B7" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>136721967</v>
       </c>
       <c r="B8" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>136721970</v>
       </c>
       <c r="B9" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>136721971</v>
       </c>
       <c r="B10" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>136721972</v>
       </c>
       <c r="B11" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136721973</v>
       </c>
       <c r="B12" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>136721974</v>
       </c>
       <c r="B13" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>136721975</v>
       </c>
       <c r="B14" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>136721976</v>
       </c>
       <c r="B15" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>136721977</v>
       </c>
       <c r="B16" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136721979</v>
       </c>
       <c r="B17" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>136721980</v>
       </c>
       <c r="B18" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>136721981</v>
       </c>
       <c r="B19" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>136721982</v>
       </c>
       <c r="B20" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>136721983</v>
       </c>
       <c r="B21" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>136721984</v>
       </c>
       <c r="B22" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>136721985</v>
       </c>
       <c r="B23" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>136721986</v>
       </c>
       <c r="B24" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 38326-2025 artfynd.xlsx
+++ b/artfynd/A 38326-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136721966</v>
       </c>
       <c r="B2" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136721987</v>
       </c>
       <c r="B3" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136721968</v>
       </c>
       <c r="B4" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136721978</v>
       </c>
       <c r="B5" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136721964</v>
       </c>
       <c r="B6" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136721965</v>
       </c>
       <c r="B7" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>136721967</v>
       </c>
       <c r="B8" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>136721970</v>
       </c>
       <c r="B9" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>136721971</v>
       </c>
       <c r="B10" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>136721972</v>
       </c>
       <c r="B11" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136721973</v>
       </c>
       <c r="B12" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>136721974</v>
       </c>
       <c r="B13" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>136721975</v>
       </c>
       <c r="B14" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>136721976</v>
       </c>
       <c r="B15" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>136721977</v>
       </c>
       <c r="B16" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136721979</v>
       </c>
       <c r="B17" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>136721980</v>
       </c>
       <c r="B18" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>136721981</v>
       </c>
       <c r="B19" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>136721982</v>
       </c>
       <c r="B20" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>136721983</v>
       </c>
       <c r="B21" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>136721984</v>
       </c>
       <c r="B22" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>136721985</v>
       </c>
       <c r="B23" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>136721986</v>
       </c>
       <c r="B24" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 38326-2025 artfynd.xlsx
+++ b/artfynd/A 38326-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136721966</v>
       </c>
       <c r="B2" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136721987</v>
       </c>
       <c r="B3" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136721968</v>
       </c>
       <c r="B4" t="n">
-        <v>93420</v>
+        <v>93433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136721978</v>
       </c>
       <c r="B5" t="n">
-        <v>93420</v>
+        <v>93433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136721964</v>
       </c>
       <c r="B6" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136721965</v>
       </c>
       <c r="B7" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>136721967</v>
       </c>
       <c r="B8" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>136721970</v>
       </c>
       <c r="B9" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>136721971</v>
       </c>
       <c r="B10" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>136721972</v>
       </c>
       <c r="B11" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136721973</v>
       </c>
       <c r="B12" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>136721974</v>
       </c>
       <c r="B13" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>136721975</v>
       </c>
       <c r="B14" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>136721976</v>
       </c>
       <c r="B15" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>136721977</v>
       </c>
       <c r="B16" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136721979</v>
       </c>
       <c r="B17" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>136721980</v>
       </c>
       <c r="B18" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>136721981</v>
       </c>
       <c r="B19" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>136721982</v>
       </c>
       <c r="B20" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>136721983</v>
       </c>
       <c r="B21" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>136721984</v>
       </c>
       <c r="B22" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>136721985</v>
       </c>
       <c r="B23" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>136721986</v>
       </c>
       <c r="B24" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 38326-2025 artfynd.xlsx
+++ b/artfynd/A 38326-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136721966</v>
       </c>
       <c r="B2" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136721987</v>
       </c>
       <c r="B3" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136721968</v>
       </c>
       <c r="B4" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136721978</v>
       </c>
       <c r="B5" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136721964</v>
       </c>
       <c r="B6" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136721965</v>
       </c>
       <c r="B7" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>136721967</v>
       </c>
       <c r="B8" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>136721970</v>
       </c>
       <c r="B9" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>136721971</v>
       </c>
       <c r="B10" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>136721972</v>
       </c>
       <c r="B11" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136721973</v>
       </c>
       <c r="B12" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>136721974</v>
       </c>
       <c r="B13" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>136721975</v>
       </c>
       <c r="B14" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>136721976</v>
       </c>
       <c r="B15" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>136721977</v>
       </c>
       <c r="B16" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136721979</v>
       </c>
       <c r="B17" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>136721980</v>
       </c>
       <c r="B18" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>136721981</v>
       </c>
       <c r="B19" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>136721982</v>
       </c>
       <c r="B20" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>136721983</v>
       </c>
       <c r="B21" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>136721984</v>
       </c>
       <c r="B22" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>136721985</v>
       </c>
       <c r="B23" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>136721986</v>
       </c>
       <c r="B24" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 38326-2025 artfynd.xlsx
+++ b/artfynd/A 38326-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136721966</v>
       </c>
       <c r="B2" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136721987</v>
       </c>
       <c r="B3" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136721968</v>
       </c>
       <c r="B4" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136721978</v>
       </c>
       <c r="B5" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136721964</v>
       </c>
       <c r="B6" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136721965</v>
       </c>
       <c r="B7" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>136721967</v>
       </c>
       <c r="B8" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>136721970</v>
       </c>
       <c r="B9" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>136721971</v>
       </c>
       <c r="B10" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>136721972</v>
       </c>
       <c r="B11" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136721973</v>
       </c>
       <c r="B12" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>136721974</v>
       </c>
       <c r="B13" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>136721975</v>
       </c>
       <c r="B14" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>136721976</v>
       </c>
       <c r="B15" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>136721977</v>
       </c>
       <c r="B16" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136721979</v>
       </c>
       <c r="B17" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>136721980</v>
       </c>
       <c r="B18" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>136721981</v>
       </c>
       <c r="B19" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>136721982</v>
       </c>
       <c r="B20" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>136721983</v>
       </c>
       <c r="B21" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>136721984</v>
       </c>
       <c r="B22" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>136721985</v>
       </c>
       <c r="B23" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>136721986</v>
       </c>
       <c r="B24" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 38326-2025 artfynd.xlsx
+++ b/artfynd/A 38326-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136721966</v>
       </c>
       <c r="B2" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136721987</v>
       </c>
       <c r="B3" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136721968</v>
       </c>
       <c r="B4" t="n">
-        <v>93437</v>
+        <v>93447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136721978</v>
       </c>
       <c r="B5" t="n">
-        <v>93437</v>
+        <v>93447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136721964</v>
       </c>
       <c r="B6" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136721965</v>
       </c>
       <c r="B7" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>136721967</v>
       </c>
       <c r="B8" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>136721970</v>
       </c>
       <c r="B9" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>136721971</v>
       </c>
       <c r="B10" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>136721972</v>
       </c>
       <c r="B11" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136721973</v>
       </c>
       <c r="B12" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>136721974</v>
       </c>
       <c r="B13" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>136721975</v>
       </c>
       <c r="B14" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>136721976</v>
       </c>
       <c r="B15" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>136721977</v>
       </c>
       <c r="B16" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136721979</v>
       </c>
       <c r="B17" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>136721980</v>
       </c>
       <c r="B18" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>136721981</v>
       </c>
       <c r="B19" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>136721982</v>
       </c>
       <c r="B20" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>136721983</v>
       </c>
       <c r="B21" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>136721984</v>
       </c>
       <c r="B22" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>136721985</v>
       </c>
       <c r="B23" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>136721986</v>
       </c>
       <c r="B24" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 38326-2025 artfynd.xlsx
+++ b/artfynd/A 38326-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136721966</v>
       </c>
       <c r="B2" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136721987</v>
       </c>
       <c r="B3" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136721968</v>
       </c>
       <c r="B4" t="n">
-        <v>93447</v>
+        <v>93448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136721978</v>
       </c>
       <c r="B5" t="n">
-        <v>93447</v>
+        <v>93448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136721964</v>
       </c>
       <c r="B6" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136721965</v>
       </c>
       <c r="B7" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>136721967</v>
       </c>
       <c r="B8" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>136721970</v>
       </c>
       <c r="B9" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>136721971</v>
       </c>
       <c r="B10" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>136721972</v>
       </c>
       <c r="B11" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136721973</v>
       </c>
       <c r="B12" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>136721974</v>
       </c>
       <c r="B13" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>136721975</v>
       </c>
       <c r="B14" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>136721976</v>
       </c>
       <c r="B15" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>136721977</v>
       </c>
       <c r="B16" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136721979</v>
       </c>
       <c r="B17" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>136721980</v>
       </c>
       <c r="B18" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>136721981</v>
       </c>
       <c r="B19" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>136721982</v>
       </c>
       <c r="B20" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>136721983</v>
       </c>
       <c r="B21" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>136721984</v>
       </c>
       <c r="B22" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>136721985</v>
       </c>
       <c r="B23" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>136721986</v>
       </c>
       <c r="B24" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
